--- a/Data/FlightPlan/FPL_10SEP26.xlsx
+++ b/Data/FlightPlan/FPL_10SEP26.xlsx
@@ -71,6 +71,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:15</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -173,9 +176,6 @@
     <t>00:15</t>
   </si>
   <si>
-    <t>07:15</t>
-  </si>
-  <si>
     <t>VN-A203</t>
   </si>
   <si>
@@ -287,606 +287,612 @@
     <t>VN-A522</t>
   </si>
   <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
     <t>DLI</t>
   </si>
   <si>
-    <t>06:10</t>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
   </si>
   <si>
     <t>07:05</t>
   </si>
   <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
     <t>08:25</t>
   </si>
   <si>
@@ -902,12 +908,6 @@
     <t>VN-A643</t>
   </si>
   <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
     <t>11:15</t>
   </si>
   <si>
@@ -1073,7 +1073,16 @@
     <t>22:50</t>
   </si>
   <si>
-    <t>VN-A663</t>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
   </si>
   <si>
     <t>VCL</t>
@@ -1082,72 +1091,60 @@
     <t>23:20</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
   </si>
   <si>
     <t>10:05</t>
   </si>
   <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1172,6 +1169,9 @@
     <t>02:05</t>
   </si>
   <si>
+    <t>VN-A699</t>
+  </si>
+  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <t>Total Record(s): 388</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 10, 2026 01:18</t>
+    <t xml:space="preserve">Generated on  Sep 10, 2026 03:27</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1800,7 +1800,9 @@
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c t="s" r="M7" s="7">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c t="s" r="A8" s="6">
@@ -1823,13 +1825,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H8" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I8" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c t="s" r="J8" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1853,16 +1855,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G9" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H9" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I9" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="J9" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1889,13 +1891,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H10" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I10" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="J10" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -1919,16 +1921,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G11" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H11" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I11" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J11" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -1961,22 +1963,22 @@
       </c>
       <c r="D13" s="7"/>
       <c t="s" r="E13" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G13" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="H13" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -1994,22 +1996,22 @@
       </c>
       <c r="D14" s="7"/>
       <c t="s" r="E14" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G14" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H14" s="8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2027,22 +2029,22 @@
       </c>
       <c r="D15" s="7"/>
       <c t="s" r="E15" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G15" s="8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="H15" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I15" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c t="s" r="J15" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -2050,7 +2052,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c t="s" r="A16" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7">
         <v>920</v>
@@ -2060,22 +2062,22 @@
       </c>
       <c r="D16" s="7"/>
       <c t="s" r="E16" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G16" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H16" s="8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c t="s" r="I16" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c t="s" r="J16" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -2108,22 +2110,22 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G18" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H18" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2141,22 +2143,22 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G19" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2174,22 +2176,22 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H20" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2197,7 +2199,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c t="s" r="A21" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="7">
         <v>884</v>
@@ -2207,22 +2209,22 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2261,7 +2263,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G23" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H23" s="8">
         <v>56</v>
@@ -2297,7 +2299,7 @@
         <v>56</v>
       </c>
       <c t="s" r="H24" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I24" s="7">
         <v>59</v>
@@ -2327,7 +2329,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H25" s="8">
         <v>61</v>
@@ -2363,7 +2365,7 @@
         <v>61</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I26" s="7">
         <v>64</v>
@@ -2408,10 +2410,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G28" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H28" s="8">
         <v>33</v>
-      </c>
-      <c t="s" r="H28" s="8">
-        <v>32</v>
       </c>
       <c t="s" r="I28" s="7">
         <v>67</v>
@@ -2441,10 +2443,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="H29" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I29" s="7">
         <v>69</v>
@@ -2474,13 +2476,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G30" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H30" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J30" s="7">
         <v>72</v>
@@ -2491,7 +2493,7 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c t="s" r="A31" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="7">
         <v>972</v>
@@ -2510,7 +2512,7 @@
         <v>71</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I31" s="7">
         <v>73</v>
@@ -2555,7 +2557,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>77</v>
@@ -2591,7 +2593,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H34" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I34" s="7">
         <v>72</v>
@@ -2605,7 +2607,7 @@
     </row>
     <row r="35" ht="15" customHeight="1">
       <c t="s" r="A35" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="7">
         <v>7614</v>
@@ -2621,7 +2623,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>81</v>
@@ -2630,7 +2632,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2669,7 +2671,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>84</v>
@@ -2705,10 +2707,10 @@
         <v>84</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="J38" s="7">
         <v>87</v>
@@ -2735,13 +2737,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H39" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>88</v>
@@ -2771,7 +2773,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>89</v>
@@ -2803,7 +2805,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>1362</v>
+        <v>1630</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
@@ -2816,16 +2818,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H42" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I42" s="7">
         <v>92</v>
       </c>
-      <c t="s" r="I42" s="7">
+      <c t="s" r="J42" s="7">
         <v>93</v>
-      </c>
-      <c t="s" r="J42" s="7">
-        <v>94</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2836,7 +2838,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>1363</v>
+        <v>1643</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
@@ -2849,16 +2851,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2882,16 +2884,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H44" s="8">
+        <v>95</v>
+      </c>
+      <c t="s" r="I44" s="7">
         <v>96</v>
       </c>
-      <c t="s" r="I44" s="7">
-        <v>97</v>
-      </c>
       <c t="s" r="J44" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2915,16 +2917,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I45" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2948,16 +2950,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H46" s="8">
+        <v>98</v>
+      </c>
+      <c t="s" r="I46" s="7">
         <v>99</v>
       </c>
-      <c t="s" r="I46" s="7">
+      <c t="s" r="J46" s="7">
         <v>100</v>
-      </c>
-      <c t="s" r="J46" s="7">
-        <v>101</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2981,16 +2983,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I47" s="7">
+        <v>101</v>
+      </c>
+      <c t="s" r="J47" s="7">
         <v>102</v>
-      </c>
-      <c t="s" r="J47" s="7">
-        <v>103</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3023,22 +3025,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
+        <v>103</v>
+      </c>
+      <c r="F49" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G49" s="8">
         <v>104</v>
       </c>
-      <c r="F49" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G49" s="8">
+      <c t="s" r="H49" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I49" s="7">
         <v>105</v>
       </c>
-      <c t="s" r="H49" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I49" s="7">
+      <c t="s" r="J49" s="7">
         <v>106</v>
-      </c>
-      <c t="s" r="J49" s="7">
-        <v>107</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3056,22 +3058,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H50" s="8">
+        <v>107</v>
+      </c>
+      <c t="s" r="I50" s="7">
         <v>108</v>
       </c>
-      <c t="s" r="I50" s="7">
+      <c t="s" r="J50" s="7">
         <v>109</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>110</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3079,7 +3081,7 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c t="s" r="A51" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="7">
         <v>821</v>
@@ -3089,22 +3091,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I51" s="7">
+        <v>110</v>
+      </c>
+      <c t="s" r="J51" s="7">
         <v>111</v>
-      </c>
-      <c t="s" r="J51" s="7">
-        <v>93</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3143,13 +3145,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>113</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>114</v>
@@ -3179,7 +3181,7 @@
         <v>113</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I54" s="7">
         <v>115</v>
@@ -3209,10 +3211,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I55" s="7">
         <v>116</v>
@@ -3242,10 +3244,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I56" s="7">
         <v>118</v>
@@ -3290,10 +3292,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I58" s="7">
         <v>121</v>
@@ -3323,7 +3325,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>123</v>
@@ -3332,7 +3334,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3359,7 +3361,7 @@
         <v>123</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>125</v>
@@ -3389,10 +3391,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I61" s="7">
         <v>127</v>
@@ -3422,13 +3424,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>129</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>130</v>
@@ -3470,7 +3472,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>132</v>
@@ -3506,7 +3508,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I65" s="7">
         <v>135</v>
@@ -3536,7 +3538,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>132</v>
@@ -3572,7 +3574,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I67" s="7">
         <v>138</v>
@@ -3602,7 +3604,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>132</v>
@@ -3638,7 +3640,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>125</v>
@@ -3668,16 +3670,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I70" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3701,16 +3703,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I71" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3734,10 +3736,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>142</v>
@@ -3782,10 +3784,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I74" s="7">
         <v>133</v>
@@ -3815,10 +3817,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I75" s="7">
         <v>146</v>
@@ -3848,10 +3850,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>148</v>
@@ -3881,13 +3883,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H77" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I77" s="7">
         <v>25</v>
-      </c>
-      <c t="s" r="H77" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I77" s="7">
-        <v>24</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>149</v>
@@ -3914,10 +3916,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>150</v>
@@ -3962,10 +3964,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I80" s="7">
         <v>153</v>
@@ -3995,7 +3997,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>123</v>
@@ -4004,7 +4006,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4031,7 +4033,7 @@
         <v>123</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I82" s="7">
         <v>155</v>
@@ -4045,7 +4047,7 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B83" s="7">
         <v>938</v>
@@ -4061,10 +4063,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H83" s="8">
         <v>33</v>
-      </c>
-      <c t="s" r="H83" s="8">
-        <v>32</v>
       </c>
       <c t="s" r="I83" s="7">
         <v>156</v>
@@ -4109,10 +4111,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I85" s="7">
         <v>74</v>
@@ -4142,10 +4144,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>160</v>
@@ -4175,7 +4177,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>132</v>
@@ -4211,7 +4213,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I88" s="7">
         <v>163</v>
@@ -4241,7 +4243,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>77</v>
@@ -4277,7 +4279,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I90" s="7">
         <v>167</v>
@@ -4307,10 +4309,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>169</v>
@@ -4340,10 +4342,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>170</v>
@@ -4388,10 +4390,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I94" s="7">
         <v>159</v>
@@ -4421,10 +4423,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I95" s="7">
         <v>161</v>
@@ -4454,13 +4456,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>173</v>
@@ -4487,13 +4489,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>174</v>
@@ -4520,10 +4522,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>175</v>
@@ -4568,10 +4570,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I100" s="7">
         <v>153</v>
@@ -4601,7 +4603,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>17</v>
@@ -4682,7 +4684,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>184</v>
@@ -4718,7 +4720,7 @@
         <v>184</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I105" s="7">
         <v>186</v>
@@ -4748,7 +4750,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>113</v>
@@ -4784,13 +4786,13 @@
         <v>113</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I107" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4814,7 +4816,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>190</v>
@@ -4850,7 +4852,7 @@
         <v>190</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>62</v>
@@ -4895,10 +4897,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>194</v>
@@ -4928,16 +4930,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4961,10 +4963,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>149</v>
@@ -4978,7 +4980,7 @@
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B114" s="7">
         <v>932</v>
@@ -4994,16 +4996,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5045,13 +5047,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>198</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5075,16 +5077,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5108,13 +5110,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>199</v>
@@ -5141,16 +5143,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5272,7 +5274,7 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B124" s="7">
         <v>918</v>
@@ -5336,10 +5338,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>153</v>
@@ -5369,10 +5371,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>58</v>
@@ -5402,13 +5404,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>212</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>213</v>
@@ -5438,7 +5440,7 @@
         <v>212</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>181</v>
@@ -5468,10 +5470,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>214</v>
@@ -5501,13 +5503,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>215</v>
@@ -5549,7 +5551,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>217</v>
@@ -5585,10 +5587,10 @@
         <v>217</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>78</v>
@@ -5615,10 +5617,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>219</v>
@@ -5648,16 +5650,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5681,7 +5683,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>220</v>
@@ -5690,7 +5692,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5698,7 +5700,7 @@
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B138" s="7">
         <v>3901</v>
@@ -5717,7 +5719,7 @@
         <v>220</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>222</v>
@@ -5762,10 +5764,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>146</v>
@@ -5795,10 +5797,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>225</v>
@@ -5828,7 +5830,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>227</v>
@@ -5845,7 +5847,7 @@
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c t="s" r="A143" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B143" s="7">
         <v>1926</v>
@@ -5864,7 +5866,7 @@
         <v>227</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>207</v>
@@ -5909,16 +5911,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I145" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J145" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="J145" s="7">
-        <v>232</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5942,7 +5944,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
@@ -5951,7 +5953,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5978,7 +5980,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>178</v>
@@ -6008,7 +6010,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>77</v>
@@ -6044,10 +6046,10 @@
         <v>77</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>213</v>
@@ -6074,13 +6076,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>132</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>88</v>
@@ -6110,7 +6112,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I151" s="7">
         <v>170</v>
@@ -6124,7 +6126,7 @@
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B152" s="7">
         <v>828</v>
@@ -6140,16 +6142,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>95</v>
+        <v>233</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6191,16 +6193,16 @@
         <v>201</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>235</v>
       </c>
       <c t="s" r="K154" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
@@ -6225,16 +6227,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6258,10 +6260,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>149</v>
@@ -6275,7 +6277,7 @@
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c t="s" r="A157" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B157" s="7">
         <v>862</v>
@@ -6291,7 +6293,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
@@ -6339,7 +6341,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>113</v>
@@ -6441,7 +6443,7 @@
         <v>113</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>243</v>
@@ -6489,10 +6491,10 @@
         <v>201</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>245</v>
@@ -6519,16 +6521,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>246</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6552,10 +6554,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>148</v>
@@ -6585,7 +6587,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>77</v>
@@ -6594,7 +6596,7 @@
         <v>247</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6621,7 +6623,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>248</v>
@@ -6666,10 +6668,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>74</v>
@@ -6699,10 +6701,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>157</v>
@@ -6732,7 +6734,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>251</v>
@@ -6768,7 +6770,7 @@
         <v>251</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>225</v>
@@ -6782,7 +6784,7 @@
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B174" s="7">
         <v>982</v>
@@ -6798,7 +6800,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>201</v>
@@ -6846,7 +6848,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>255</v>
@@ -6882,10 +6884,10 @@
         <v>255</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>186</v>
@@ -6912,16 +6914,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>132</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6948,7 +6950,7 @@
         <v>132</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I179" s="7">
         <v>147</v>
@@ -6978,7 +6980,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>84</v>
@@ -7014,10 +7016,10 @@
         <v>84</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>258</v>
@@ -7044,7 +7046,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>259</v>
@@ -7080,7 +7082,7 @@
         <v>259</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>260</v>
@@ -7128,10 +7130,10 @@
         <v>262</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>263</v>
@@ -7158,10 +7160,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>148</v>
@@ -7191,10 +7193,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>264</v>
@@ -7224,10 +7226,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>258</v>
@@ -7257,10 +7259,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>266</v>
@@ -7274,7 +7276,7 @@
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B190" s="7">
         <v>960</v>
@@ -7290,13 +7292,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>67</v>
@@ -7338,7 +7340,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>77</v>
@@ -7374,7 +7376,7 @@
         <v>77</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>122</v>
@@ -7404,7 +7406,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>217</v>
@@ -7440,7 +7442,7 @@
         <v>217</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>164</v>
@@ -7470,16 +7472,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7503,10 +7505,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>270</v>
@@ -7536,10 +7538,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>127</v>
@@ -7569,10 +7571,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>272</v>
@@ -7617,10 +7619,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>65</v>
@@ -7650,10 +7652,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>160</v>
@@ -7683,13 +7685,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>263</v>
@@ -7716,10 +7718,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>137</v>
@@ -7749,13 +7751,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>204</v>
@@ -7785,10 +7787,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>226</v>
@@ -7815,16 +7817,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7832,7 +7834,7 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B208" s="7">
         <v>8021</v>
@@ -7848,16 +7850,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7890,16 +7892,16 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>160</v>
@@ -7923,19 +7925,19 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>245</v>
@@ -7956,22 +7958,22 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7989,19 +7991,19 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>59</v>
@@ -8022,13 +8024,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>255</v>
@@ -8055,7 +8057,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8064,7 +8066,7 @@
         <v>255</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>181</v>
@@ -8088,19 +8090,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>182</v>
@@ -8111,7 +8113,7 @@
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B217" s="7">
         <v>7527</v>
@@ -8121,22 +8123,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8169,7 +8171,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8184,7 +8186,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8202,7 +8204,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8214,7 +8216,7 @@
         <v>212</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>138</v>
@@ -8235,7 +8237,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8244,10 +8246,10 @@
         <v>212</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>173</v>
@@ -8268,19 +8270,19 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>212</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>270</v>
@@ -8301,7 +8303,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8334,7 +8336,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8382,13 +8384,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>212</v>
@@ -8415,7 +8417,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8424,10 +8426,10 @@
         <v>212</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>124</v>
@@ -8448,16 +8450,16 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>165</v>
@@ -8481,22 +8483,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8514,16 +8516,16 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>221</v>
@@ -8547,22 +8549,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8595,22 +8597,22 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>94</v>
+        <v>293</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8628,22 +8630,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8661,13 +8663,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>84</v>
@@ -8694,7 +8696,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8703,10 +8705,10 @@
         <v>84</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>189</v>
@@ -8727,16 +8729,16 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>247</v>
@@ -8760,16 +8762,16 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>191</v>
@@ -8793,22 +8795,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>92</v>
+        <v>275</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>206</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8834,29 +8836,29 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>1630</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8867,29 +8869,29 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>1643</v>
+        <v>1363</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8907,13 +8909,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>251</v>
@@ -8940,7 +8942,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8949,7 +8951,7 @@
         <v>251</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>139</v>
@@ -8973,13 +8975,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>84</v>
@@ -9006,7 +9008,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9015,7 +9017,7 @@
         <v>84</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>155</v>
@@ -9039,16 +9041,16 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>301</v>
@@ -9093,7 +9095,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>123</v>
@@ -9129,7 +9131,7 @@
         <v>123</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>304</v>
@@ -9159,16 +9161,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9192,16 +9194,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>149</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9240,13 +9242,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>78</v>
@@ -9276,10 +9278,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>87</v>
@@ -9306,7 +9308,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>306</v>
@@ -9342,7 +9344,7 @@
         <v>306</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>180</v>
@@ -9372,7 +9374,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>306</v>
@@ -9408,7 +9410,7 @@
         <v>306</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>307</v>
@@ -9453,7 +9455,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>259</v>
@@ -9489,10 +9491,10 @@
         <v>259</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>246</v>
@@ -9519,16 +9521,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>154</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9552,16 +9554,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>180</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9600,7 +9602,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>113</v>
@@ -9636,7 +9638,7 @@
         <v>113</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>191</v>
@@ -9681,7 +9683,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>259</v>
@@ -9783,7 +9785,7 @@
         <v>259</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>187</v>
@@ -9813,7 +9815,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>259</v>
@@ -9849,7 +9851,7 @@
         <v>259</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>199</v>
@@ -9879,10 +9881,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>314</v>
@@ -9896,7 +9898,7 @@
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B276" s="7">
         <v>3909</v>
@@ -9912,10 +9914,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>316</v>
@@ -9960,16 +9962,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>319</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>231</v>
+        <v>94</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9993,7 +9995,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>212</v>
@@ -10068,7 +10070,7 @@
         <v>247</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10095,13 +10097,13 @@
         <v>212</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10140,7 +10142,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>184</v>
@@ -10176,7 +10178,7 @@
         <v>184</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>313</v>
@@ -10206,7 +10208,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
@@ -10242,7 +10244,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>59</v>
@@ -10272,7 +10274,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>217</v>
@@ -10308,7 +10310,7 @@
         <v>217</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>62</v>
@@ -10353,10 +10355,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>325</v>
@@ -10386,10 +10388,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>86</v>
@@ -10419,10 +10421,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>327</v>
@@ -10452,16 +10454,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10485,10 +10487,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>213</v>
@@ -10518,10 +10520,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>249</v>
@@ -10569,13 +10571,13 @@
         <v>330</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10599,7 +10601,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>251</v>
@@ -10635,7 +10637,7 @@
         <v>251</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>170</v>
@@ -10665,10 +10667,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>64</v>
@@ -10716,7 +10718,7 @@
         <v>332</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I303" s="7">
         <v>136</v>
@@ -10746,7 +10748,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>251</v>
@@ -10782,7 +10784,7 @@
         <v>251</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>116</v>
@@ -10812,7 +10814,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>220</v>
@@ -10829,7 +10831,7 @@
     </row>
     <row r="307" ht="14.25" customHeight="1">
       <c t="s" r="A307" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B307" s="7">
         <v>7239</v>
@@ -10848,7 +10850,7 @@
         <v>220</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>334</v>
@@ -10893,16 +10895,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>253</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>95</v>
+        <v>233</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10926,16 +10928,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I310" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10959,10 +10961,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>147</v>
@@ -10992,10 +10994,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>178</v>
@@ -11025,16 +11027,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11058,10 +11060,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>116</v>
@@ -11091,10 +11093,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>237</v>
@@ -11139,7 +11141,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>217</v>
@@ -11175,13 +11177,13 @@
         <v>217</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>326</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11205,7 +11207,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
@@ -11241,7 +11243,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>167</v>
@@ -11271,7 +11273,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>77</v>
@@ -11307,13 +11309,13 @@
         <v>77</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11352,10 +11354,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>134</v>
@@ -11385,16 +11387,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>219</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11418,13 +11420,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>251</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>341</v>
@@ -11454,7 +11456,7 @@
         <v>251</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>141</v>
@@ -11484,7 +11486,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>342</v>
@@ -11493,7 +11495,7 @@
         <v>226</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11520,7 +11522,7 @@
         <v>342</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>301</v>
@@ -11565,7 +11567,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>113</v>
@@ -11574,7 +11576,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11601,7 +11603,7 @@
         <v>113</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>299</v>
@@ -11631,16 +11633,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11664,7 +11666,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>184</v>
@@ -11700,10 +11702,10 @@
         <v>184</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>346</v>
@@ -11730,7 +11732,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>212</v>
@@ -11766,7 +11768,7 @@
         <v>212</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I337" s="7">
         <v>347</v>
@@ -11811,7 +11813,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>350</v>
@@ -11820,7 +11822,7 @@
         <v>351</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11847,13 +11849,13 @@
         <v>350</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11877,13 +11879,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>352</v>
@@ -11910,10 +11912,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>271</v>
@@ -11945,7 +11947,7 @@
         <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>126</v>
+        <v>809</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
@@ -11955,19 +11957,19 @@
         <v>354</v>
       </c>
       <c r="F344" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11978,7 +11980,7 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>131</v>
+        <v>808</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
@@ -11988,19 +11990,19 @@
         <v>354</v>
       </c>
       <c r="F345" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12011,7 +12013,7 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>374</v>
+        <v>876</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
@@ -12021,19 +12023,19 @@
         <v>354</v>
       </c>
       <c r="F346" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12044,7 +12046,7 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>375</v>
+        <v>877</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
@@ -12054,53 +12056,35 @@
         <v>354</v>
       </c>
       <c r="F347" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>341</v>
+        <v>170</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>264</v>
+        <v>206</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c t="s" r="A348" s="6">
-        <v>13</v>
-      </c>
-      <c r="B348" s="7">
-        <v>384</v>
-      </c>
-      <c t="s" r="C348" s="7">
-        <v>14</v>
-      </c>
+      <c r="A348" s="6"/>
+      <c r="B348" s="7"/>
+      <c r="C348" s="7"/>
       <c r="D348" s="7"/>
-      <c t="s" r="E348" s="7">
-        <v>354</v>
-      </c>
-      <c r="F348" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G348" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H348" s="8">
-        <v>255</v>
-      </c>
-      <c t="s" r="I348" s="7">
-        <v>174</v>
-      </c>
-      <c t="s" r="J348" s="7">
-        <v>181</v>
-      </c>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
+      <c r="G348" s="8"/>
+      <c r="H348" s="8"/>
+      <c r="I348" s="7"/>
+      <c r="J348" s="7"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
@@ -12110,29 +12094,29 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>385</v>
+        <v>126</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>255</v>
+        <v>26</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>127</v>
+        <v>239</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12143,29 +12127,29 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>1312</v>
+        <v>131</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>237</v>
+        <v>36</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12176,45 +12160,63 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>1311</v>
+        <v>374</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>25</v>
+        <v>358</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>307</v>
+        <v>106</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>356</v>
+        <v>188</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
-      <c r="A352" s="6"/>
-      <c r="B352" s="7"/>
-      <c r="C352" s="7"/>
+      <c t="s" r="A352" s="6">
+        <v>13</v>
+      </c>
+      <c r="B352" s="7">
+        <v>375</v>
+      </c>
+      <c t="s" r="C352" s="7">
+        <v>14</v>
+      </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="8"/>
-      <c r="H352" s="8"/>
-      <c r="I352" s="7"/>
-      <c r="J352" s="7"/>
+      <c t="s" r="E352" s="7">
+        <v>357</v>
+      </c>
+      <c r="F352" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G352" s="8">
+        <v>358</v>
+      </c>
+      <c t="s" r="H352" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I352" s="7">
+        <v>341</v>
+      </c>
+      <c t="s" r="J352" s="7">
+        <v>264</v>
+      </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
@@ -12224,7 +12226,7 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>809</v>
+        <v>384</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
@@ -12234,19 +12236,19 @@
         <v>357</v>
       </c>
       <c r="F353" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12257,7 +12259,7 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>808</v>
+        <v>385</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
@@ -12267,19 +12269,19 @@
         <v>357</v>
       </c>
       <c r="F354" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12290,7 +12292,7 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>876</v>
+        <v>1312</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
@@ -12300,19 +12302,19 @@
         <v>357</v>
       </c>
       <c r="F355" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12323,7 +12325,7 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>877</v>
+        <v>1311</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
@@ -12333,19 +12335,19 @@
         <v>357</v>
       </c>
       <c r="F356" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
+        <v>132</v>
+      </c>
+      <c t="s" r="H356" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I356" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="J356" s="7">
         <v>359</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>170</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>206</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12371,7 +12373,7 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>801</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
@@ -12384,16 +12386,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>251</v>
+        <v>358</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>361</v>
+        <v>185</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12404,7 +12406,7 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>802</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
@@ -12417,16 +12419,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>251</v>
+        <v>358</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12437,7 +12439,7 @@
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
@@ -12450,16 +12452,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>212</v>
+        <v>358</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12470,7 +12472,7 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
@@ -12483,32 +12485,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>212</v>
+        <v>358</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c r="M361" s="7"/>
     </row>
     <row r="362" ht="14.25" customHeight="1">
-      <c r="A362" s="6"/>
-      <c r="B362" s="7"/>
-      <c r="C362" s="7"/>
+      <c t="s" r="A362" s="6">
+        <v>13</v>
+      </c>
+      <c r="B362" s="7">
+        <v>376</v>
+      </c>
+      <c t="s" r="C362" s="7">
+        <v>14</v>
+      </c>
       <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
-      <c r="G362" s="8"/>
-      <c r="H362" s="8"/>
-      <c r="I362" s="7"/>
-      <c r="J362" s="7"/>
+      <c t="s" r="E362" s="7">
+        <v>360</v>
+      </c>
+      <c r="F362" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G362" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H362" s="8">
+        <v>358</v>
+      </c>
+      <c t="s" r="I362" s="7">
+        <v>24</v>
+      </c>
+      <c t="s" r="J362" s="7">
+        <v>69</v>
+      </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
@@ -12518,29 +12538,29 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>1372</v>
+        <v>377</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>25</v>
+        <v>358</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>355</v>
+        <v>26</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>185</v>
+        <v>362</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12551,29 +12571,29 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>1373</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>355</v>
+        <v>26</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>25</v>
+        <v>363</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12581,66 +12601,48 @@
     </row>
     <row r="365" ht="15" customHeight="1">
       <c t="s" r="A365" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B365" s="7">
-        <v>372</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>25</v>
+        <v>363</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>355</v>
+        <v>26</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c t="s" r="A366" s="6">
-        <v>13</v>
-      </c>
-      <c r="B366" s="7">
-        <v>373</v>
-      </c>
-      <c t="s" r="C366" s="7">
-        <v>14</v>
-      </c>
+      <c r="A366" s="6"/>
+      <c r="B366" s="7"/>
+      <c r="C366" s="7"/>
       <c r="D366" s="7"/>
-      <c t="s" r="E366" s="7">
-        <v>362</v>
-      </c>
-      <c r="F366" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G366" s="8">
-        <v>355</v>
-      </c>
-      <c t="s" r="H366" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I366" s="7">
-        <v>187</v>
-      </c>
-      <c t="s" r="J366" s="7">
-        <v>48</v>
-      </c>
+      <c r="E366" s="7"/>
+      <c r="F366" s="7"/>
+      <c r="G366" s="8"/>
+      <c r="H366" s="8"/>
+      <c r="I366" s="7"/>
+      <c r="J366" s="7"/>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
@@ -12650,29 +12652,29 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>376</v>
+        <v>879</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F367" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>355</v>
+        <v>29</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12683,29 +12685,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>377</v>
+        <v>8512</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F368" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>355</v>
+        <v>29</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>364</v>
+        <v>125</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12716,29 +12718,29 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>3948</v>
+        <v>8513</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F369" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>365</v>
+        <v>29</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12746,32 +12748,32 @@
     </row>
     <row r="370" ht="15" customHeight="1">
       <c t="s" r="A370" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B370" s="7">
-        <v>3949</v>
+        <v>988</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F370" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>365</v>
+        <v>29</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>25</v>
+        <v>201</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>252</v>
+        <v>90</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12797,29 +12799,29 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>879</v>
+        <v>849</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>239</v>
+        <v>106</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12830,29 +12832,29 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>8512</v>
+        <v>848</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12863,29 +12865,29 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>8513</v>
+        <v>352</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c t="s" r="H374" s="8">
+        <v>217</v>
+      </c>
+      <c t="s" r="I374" s="7">
+        <v>345</v>
+      </c>
+      <c t="s" r="J374" s="7">
         <v>28</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>213</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>149</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12893,32 +12895,32 @@
     </row>
     <row r="375" ht="15" customHeight="1">
       <c t="s" r="A375" s="6">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>988</v>
+        <v>353</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>185</v>
+        <v>333</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12944,29 +12946,29 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>849</v>
+        <v>401</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F377" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12977,29 +12979,29 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>848</v>
+        <v>798</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F378" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13010,29 +13012,29 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>352</v>
+        <v>799</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F379" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13043,45 +13045,63 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>353</v>
+        <v>402</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F380" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>333</v>
+        <v>189</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c r="A381" s="6"/>
-      <c r="B381" s="7"/>
-      <c r="C381" s="7"/>
+      <c t="s" r="A381" s="6">
+        <v>13</v>
+      </c>
+      <c r="B381" s="7">
+        <v>441</v>
+      </c>
+      <c t="s" r="C381" s="7">
+        <v>14</v>
+      </c>
       <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
-      <c r="F381" s="7"/>
-      <c r="G381" s="8"/>
-      <c r="H381" s="8"/>
-      <c r="I381" s="7"/>
-      <c r="J381" s="7"/>
+      <c t="s" r="E381" s="7">
+        <v>366</v>
+      </c>
+      <c r="F381" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G381" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H381" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I381" s="7">
+        <v>323</v>
+      </c>
+      <c t="s" r="J381" s="7">
+        <v>155</v>
+      </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
@@ -13091,63 +13111,45 @@
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>86</v>
+        <v>237</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
-      <c t="s" r="A383" s="6">
-        <v>13</v>
-      </c>
-      <c r="B383" s="7">
-        <v>798</v>
-      </c>
-      <c t="s" r="C383" s="7">
-        <v>14</v>
-      </c>
+      <c r="A383" s="6"/>
+      <c r="B383" s="7"/>
+      <c r="C383" s="7"/>
       <c r="D383" s="7"/>
-      <c t="s" r="E383" s="7">
-        <v>368</v>
-      </c>
-      <c r="F383" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G383" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H383" s="8">
-        <v>259</v>
-      </c>
-      <c t="s" r="I383" s="7">
-        <v>34</v>
-      </c>
-      <c t="s" r="J383" s="7">
-        <v>162</v>
-      </c>
+      <c r="E383" s="7"/>
+      <c r="F383" s="7"/>
+      <c r="G383" s="8"/>
+      <c r="H383" s="8"/>
+      <c r="I383" s="7"/>
+      <c r="J383" s="7"/>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c r="M383" s="7"/>
@@ -13157,29 +13159,29 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>799</v>
+        <v>120</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>259</v>
+        <v>26</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>163</v>
+        <v>311</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13190,29 +13192,29 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13223,29 +13225,29 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13256,78 +13258,78 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>33</v>
+        <v>275</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>127</v>
+        <v>225</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="6"/>
-      <c r="B388" s="7"/>
-      <c r="C388" s="7"/>
+      <c t="s" r="A388" s="6">
+        <v>13</v>
+      </c>
+      <c r="B388" s="7">
+        <v>408</v>
+      </c>
+      <c t="s" r="C388" s="7">
+        <v>14</v>
+      </c>
       <c r="D388" s="7"/>
-      <c r="E388" s="7"/>
-      <c r="F388" s="7"/>
-      <c r="G388" s="8"/>
-      <c r="H388" s="8"/>
-      <c r="I388" s="7"/>
-      <c r="J388" s="7"/>
+      <c t="s" r="E388" s="7">
+        <v>367</v>
+      </c>
+      <c r="F388" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G388" s="8">
+        <v>275</v>
+      </c>
+      <c t="s" r="H388" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I388" s="7">
+        <v>199</v>
+      </c>
+      <c t="s" r="J388" s="7">
+        <v>258</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c t="s" r="A389" s="6">
-        <v>13</v>
-      </c>
-      <c r="B389" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="C389" s="7">
-        <v>14</v>
-      </c>
+      <c r="A389" s="6"/>
+      <c r="B389" s="7"/>
+      <c r="C389" s="7"/>
       <c r="D389" s="7"/>
-      <c t="s" r="E389" s="7">
-        <v>369</v>
-      </c>
-      <c r="F389" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G389" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H389" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I389" s="7">
-        <v>311</v>
-      </c>
-      <c t="s" r="J389" s="7">
-        <v>253</v>
-      </c>
+      <c r="E389" s="7"/>
+      <c r="F389" s="7"/>
+      <c r="G389" s="8"/>
+      <c r="H389" s="8"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7"/>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c r="M389" s="7"/>
@@ -13337,29 +13339,29 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>447</v>
+        <v>925</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F390" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13370,29 +13372,29 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>440</v>
+        <v>671</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F391" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13403,29 +13405,29 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>407</v>
+        <v>670</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F392" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>225</v>
+        <v>154</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>180</v>
+        <v>341</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13436,45 +13438,63 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
+        <v>368</v>
+      </c>
+      <c r="F393" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G393" s="8">
+        <v>212</v>
+      </c>
+      <c t="s" r="H393" s="8">
         <v>369</v>
       </c>
-      <c r="F393" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G393" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H393" s="8">
-        <v>33</v>
-      </c>
       <c t="s" r="I393" s="7">
-        <v>199</v>
+        <v>97</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>258</v>
+        <v>362</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c r="M393" s="7"/>
     </row>
     <row r="394" ht="14.25" customHeight="1">
-      <c r="A394" s="6"/>
-      <c r="B394" s="7"/>
-      <c r="C394" s="7"/>
+      <c t="s" r="A394" s="6">
+        <v>13</v>
+      </c>
+      <c r="B394" s="7">
+        <v>488</v>
+      </c>
+      <c t="s" r="C394" s="7">
+        <v>14</v>
+      </c>
       <c r="D394" s="7"/>
-      <c r="E394" s="7"/>
-      <c r="F394" s="7"/>
-      <c r="G394" s="8"/>
-      <c r="H394" s="8"/>
-      <c r="I394" s="7"/>
-      <c r="J394" s="7"/>
+      <c t="s" r="E394" s="7">
+        <v>368</v>
+      </c>
+      <c r="F394" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G394" s="8">
+        <v>369</v>
+      </c>
+      <c t="s" r="H394" s="8">
+        <v>212</v>
+      </c>
+      <c t="s" r="I394" s="7">
+        <v>27</v>
+      </c>
+      <c t="s" r="J394" s="7">
+        <v>170</v>
+      </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
@@ -13484,63 +13504,45 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
+        <v>368</v>
+      </c>
+      <c r="F395" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G395" s="8">
+        <v>212</v>
+      </c>
+      <c t="s" r="H395" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I395" s="7">
         <v>370</v>
       </c>
-      <c r="F395" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G395" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H395" s="8">
-        <v>212</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>54</v>
-      </c>
       <c t="s" r="J395" s="7">
-        <v>269</v>
+        <v>351</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c t="s" r="A396" s="6">
-        <v>13</v>
-      </c>
-      <c r="B396" s="7">
-        <v>671</v>
-      </c>
-      <c t="s" r="C396" s="7">
-        <v>14</v>
-      </c>
+      <c r="A396" s="6"/>
+      <c r="B396" s="7"/>
+      <c r="C396" s="7"/>
       <c r="D396" s="7"/>
-      <c t="s" r="E396" s="7">
-        <v>370</v>
-      </c>
-      <c r="F396" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G396" s="8">
-        <v>212</v>
-      </c>
-      <c t="s" r="H396" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="I396" s="7">
-        <v>202</v>
-      </c>
-      <c t="s" r="J396" s="7">
-        <v>211</v>
-      </c>
+      <c r="E396" s="7"/>
+      <c r="F396" s="7"/>
+      <c r="G396" s="8"/>
+      <c r="H396" s="8"/>
+      <c r="I396" s="7"/>
+      <c r="J396" s="7"/>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
@@ -13550,29 +13552,29 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>670</v>
+        <v>1625</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13583,29 +13585,29 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>489</v>
+        <v>634</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>371</v>
+        <v>29</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>364</v>
+        <v>241</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13616,29 +13618,29 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>488</v>
+        <v>973</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>371</v>
+        <v>29</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>212</v>
+        <v>113</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>26</v>
+        <v>344</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13649,111 +13651,111 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>926</v>
+        <v>814</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>212</v>
+        <v>113</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>351</v>
+        <v>149</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c r="M400" s="7"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="6"/>
-      <c r="B401" s="7"/>
-      <c r="C401" s="7"/>
+      <c t="s" r="A401" s="6">
+        <v>13</v>
+      </c>
+      <c r="B401" s="7">
+        <v>858</v>
+      </c>
+      <c t="s" r="C401" s="7">
+        <v>14</v>
+      </c>
       <c r="D401" s="7"/>
-      <c r="E401" s="7"/>
-      <c r="F401" s="7"/>
-      <c r="G401" s="8"/>
-      <c r="H401" s="8"/>
-      <c r="I401" s="7"/>
-      <c r="J401" s="7"/>
+      <c t="s" r="E401" s="7">
+        <v>371</v>
+      </c>
+      <c r="F401" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G401" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H401" s="8">
+        <v>276</v>
+      </c>
+      <c t="s" r="I401" s="7">
+        <v>372</v>
+      </c>
+      <c t="s" r="J401" s="7">
+        <v>283</v>
+      </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c t="s" r="A402" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B402" s="7">
-        <v>1625</v>
+        <v>859</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
+        <v>371</v>
+      </c>
+      <c r="F402" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G402" s="8">
+        <v>276</v>
+      </c>
+      <c t="s" r="H402" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I402" s="7">
         <v>373</v>
       </c>
-      <c r="F402" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G402" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="H402" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I402" s="7">
-        <v>145</v>
-      </c>
       <c t="s" r="J402" s="7">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c t="s" r="A403" s="6">
-        <v>13</v>
-      </c>
-      <c r="B403" s="7">
-        <v>634</v>
-      </c>
-      <c t="s" r="C403" s="7">
-        <v>14</v>
-      </c>
+      <c r="A403" s="6"/>
+      <c r="B403" s="7"/>
+      <c r="C403" s="7"/>
       <c r="D403" s="7"/>
-      <c t="s" r="E403" s="7">
-        <v>373</v>
-      </c>
-      <c r="F403" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G403" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H403" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="I403" s="7">
-        <v>79</v>
-      </c>
-      <c t="s" r="J403" s="7">
-        <v>241</v>
-      </c>
+      <c r="E403" s="7"/>
+      <c r="F403" s="7"/>
+      <c r="G403" s="8"/>
+      <c r="H403" s="8"/>
+      <c r="I403" s="7"/>
+      <c r="J403" s="7"/>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c r="M403" s="7"/>
@@ -13763,29 +13765,29 @@
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>344</v>
+        <v>235</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>270</v>
+        <v>58</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13796,29 +13798,29 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>814</v>
+        <v>145</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c t="s" r="H405" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I405" s="7">
+        <v>173</v>
+      </c>
+      <c t="s" r="J405" s="7">
         <v>25</v>
-      </c>
-      <c t="s" r="I405" s="7">
-        <v>345</v>
-      </c>
-      <c t="s" r="J405" s="7">
-        <v>149</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13829,78 +13831,78 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>858</v>
+        <v>150</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>275</v>
+        <v>34</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>374</v>
+        <v>126</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>282</v>
+        <v>41</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c r="M406" s="7"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c t="s" r="A407" s="6">
-        <v>41</v>
-      </c>
-      <c r="B407" s="7">
-        <v>859</v>
-      </c>
-      <c t="s" r="C407" s="7">
-        <v>14</v>
-      </c>
+      <c r="A407" s="6"/>
+      <c r="B407" s="7"/>
+      <c r="C407" s="7"/>
       <c r="D407" s="7"/>
-      <c t="s" r="E407" s="7">
-        <v>373</v>
-      </c>
-      <c r="F407" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G407" s="8">
-        <v>275</v>
-      </c>
-      <c t="s" r="H407" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I407" s="7">
-        <v>375</v>
-      </c>
-      <c t="s" r="J407" s="7">
-        <v>376</v>
-      </c>
+      <c r="E407" s="7"/>
+      <c r="F407" s="7"/>
+      <c r="G407" s="8"/>
+      <c r="H407" s="8"/>
+      <c r="I407" s="7"/>
+      <c r="J407" s="7"/>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c r="M407" s="7"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c r="A408" s="6"/>
-      <c r="B408" s="7"/>
-      <c r="C408" s="7"/>
+      <c t="s" r="A408" s="6">
+        <v>13</v>
+      </c>
+      <c r="B408" s="7">
+        <v>382</v>
+      </c>
+      <c t="s" r="C408" s="7">
+        <v>14</v>
+      </c>
       <c r="D408" s="7"/>
-      <c r="E408" s="7"/>
-      <c r="F408" s="7"/>
-      <c r="G408" s="8"/>
-      <c r="H408" s="8"/>
-      <c r="I408" s="7"/>
-      <c r="J408" s="7"/>
+      <c t="s" r="E408" s="7">
+        <v>376</v>
+      </c>
+      <c r="F408" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G408" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H408" s="8">
+        <v>255</v>
+      </c>
+      <c t="s" r="I408" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J408" s="7">
+        <v>48</v>
+      </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c r="M408" s="7"/>
@@ -13910,29 +13912,29 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>961</v>
+        <v>383</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
+        <v>376</v>
+      </c>
+      <c r="F409" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G409" s="8">
+        <v>255</v>
+      </c>
+      <c t="s" r="H409" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I409" s="7">
         <v>377</v>
       </c>
-      <c r="F409" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G409" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H409" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I409" s="7">
-        <v>235</v>
-      </c>
       <c t="s" r="J409" s="7">
-        <v>58</v>
+        <v>187</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13943,26 +13945,26 @@
         <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>24</v>
@@ -13976,78 +13978,78 @@
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>150</v>
+        <v>465</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>33</v>
+        <v>369</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c r="M411" s="7"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
-      <c r="A412" s="6"/>
-      <c r="B412" s="7"/>
-      <c r="C412" s="7"/>
+      <c t="s" r="A412" s="6">
+        <v>13</v>
+      </c>
+      <c r="B412" s="7">
+        <v>466</v>
+      </c>
+      <c t="s" r="C412" s="7">
+        <v>14</v>
+      </c>
       <c r="D412" s="7"/>
-      <c r="E412" s="7"/>
-      <c r="F412" s="7"/>
-      <c r="G412" s="8"/>
-      <c r="H412" s="8"/>
-      <c r="I412" s="7"/>
-      <c r="J412" s="7"/>
+      <c t="s" r="E412" s="7">
+        <v>376</v>
+      </c>
+      <c r="F412" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G412" s="8">
+        <v>369</v>
+      </c>
+      <c t="s" r="H412" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I412" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J412" s="7">
+        <v>291</v>
+      </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c r="M412" s="7"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
-      <c t="s" r="A413" s="6">
-        <v>13</v>
-      </c>
-      <c r="B413" s="7">
-        <v>382</v>
-      </c>
-      <c t="s" r="C413" s="7">
-        <v>14</v>
-      </c>
+      <c r="A413" s="6"/>
+      <c r="B413" s="7"/>
+      <c r="C413" s="7"/>
       <c r="D413" s="7"/>
-      <c t="s" r="E413" s="7">
-        <v>378</v>
-      </c>
-      <c r="F413" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G413" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H413" s="8">
-        <v>255</v>
-      </c>
-      <c t="s" r="I413" s="7">
-        <v>292</v>
-      </c>
-      <c t="s" r="J413" s="7">
-        <v>47</v>
-      </c>
+      <c r="E413" s="7"/>
+      <c r="F413" s="7"/>
+      <c r="G413" s="8"/>
+      <c r="H413" s="8"/>
+      <c r="I413" s="7"/>
+      <c r="J413" s="7"/>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c r="M413" s="7"/>
@@ -14057,7 +14059,7 @@
         <v>13</v>
       </c>
       <c r="B414" s="7">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c t="s" r="C414" s="7">
         <v>14</v>
@@ -14067,19 +14069,19 @@
         <v>378</v>
       </c>
       <c r="F414" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H414" s="8">
         <v>255</v>
       </c>
-      <c t="s" r="H414" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I414" s="7">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14090,7 +14092,7 @@
         <v>13</v>
       </c>
       <c r="B415" s="7">
-        <v>136</v>
+        <v>430</v>
       </c>
       <c t="s" r="C415" s="7">
         <v>14</v>
@@ -14100,19 +14102,19 @@
         <v>378</v>
       </c>
       <c r="F415" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>25</v>
+        <v>255</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14123,7 +14125,7 @@
         <v>13</v>
       </c>
       <c r="B416" s="7">
-        <v>465</v>
+        <v>403</v>
       </c>
       <c t="s" r="C416" s="7">
         <v>14</v>
@@ -14133,19 +14135,19 @@
         <v>378</v>
       </c>
       <c r="F416" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14156,7 +14158,7 @@
         <v>13</v>
       </c>
       <c r="B417" s="7">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c t="s" r="C417" s="7">
         <v>14</v>
@@ -14166,35 +14168,53 @@
         <v>378</v>
       </c>
       <c r="F417" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>371</v>
+        <v>275</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c r="M417" s="7"/>
     </row>
     <row r="418" ht="14.25" customHeight="1">
-      <c r="A418" s="6"/>
-      <c r="B418" s="7"/>
-      <c r="C418" s="7"/>
+      <c t="s" r="A418" s="6">
+        <v>13</v>
+      </c>
+      <c r="B418" s="7">
+        <v>423</v>
+      </c>
+      <c t="s" r="C418" s="7">
+        <v>14</v>
+      </c>
       <c r="D418" s="7"/>
-      <c r="E418" s="7"/>
-      <c r="F418" s="7"/>
-      <c r="G418" s="8"/>
-      <c r="H418" s="8"/>
-      <c r="I418" s="7"/>
-      <c r="J418" s="7"/>
+      <c t="s" r="E418" s="7">
+        <v>378</v>
+      </c>
+      <c r="F418" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G418" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H418" s="8">
+        <v>184</v>
+      </c>
+      <c t="s" r="I418" s="7">
+        <v>166</v>
+      </c>
+      <c t="s" r="J418" s="7">
+        <v>50</v>
+      </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c r="M418" s="7"/>
@@ -14204,29 +14224,29 @@
         <v>13</v>
       </c>
       <c r="B419" s="7">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14237,29 +14257,29 @@
         <v>13</v>
       </c>
       <c r="B420" s="7">
-        <v>430</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C420" s="7">
         <v>14</v>
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>209</v>
+        <v>379</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14267,66 +14287,48 @@
     </row>
     <row r="421" ht="14.25" customHeight="1">
       <c t="s" r="A421" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B421" s="7">
-        <v>403</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>33</v>
+        <v>363</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>256</v>
+        <v>380</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c r="M421" s="7"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c t="s" r="A422" s="6">
-        <v>13</v>
-      </c>
-      <c r="B422" s="7">
-        <v>404</v>
-      </c>
-      <c t="s" r="C422" s="7">
-        <v>14</v>
-      </c>
+      <c r="A422" s="6"/>
+      <c r="B422" s="7"/>
+      <c r="C422" s="7"/>
       <c r="D422" s="7"/>
-      <c t="s" r="E422" s="7">
-        <v>379</v>
-      </c>
-      <c r="F422" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G422" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H422" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I422" s="7">
-        <v>164</v>
-      </c>
-      <c t="s" r="J422" s="7">
-        <v>140</v>
-      </c>
+      <c r="E422" s="7"/>
+      <c r="F422" s="7"/>
+      <c r="G422" s="8"/>
+      <c r="H422" s="8"/>
+      <c r="I422" s="7"/>
+      <c r="J422" s="7"/>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c r="M422" s="7"/>
@@ -14336,29 +14338,29 @@
         <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>423</v>
+        <v>969</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F423" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>166</v>
+        <v>338</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>49</v>
+        <v>187</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14369,29 +14371,29 @@
         <v>13</v>
       </c>
       <c r="B424" s="7">
-        <v>424</v>
+        <v>986</v>
       </c>
       <c t="s" r="C424" s="7">
         <v>14</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F424" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14402,29 +14404,29 @@
         <v>13</v>
       </c>
       <c r="B425" s="7">
-        <v>7712</v>
+        <v>985</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F425" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>365</v>
+        <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>380</v>
+        <v>100</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14432,32 +14434,32 @@
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c t="s" r="A426" s="6">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B426" s="7">
-        <v>7713</v>
+        <v>322</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F426" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>365</v>
+        <v>17</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14483,7 +14485,7 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>969</v>
+        <v>720</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
@@ -14496,16 +14498,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14516,7 +14518,7 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>986</v>
+        <v>721</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
@@ -14529,16 +14531,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>359</v>
+        <v>29</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>246</v>
+        <v>87</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14549,7 +14551,7 @@
         <v>13</v>
       </c>
       <c r="B430" s="7">
-        <v>985</v>
+        <v>703</v>
       </c>
       <c t="s" r="C430" s="7">
         <v>14</v>
@@ -14562,16 +14564,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>359</v>
+        <v>29</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>17</v>
+        <v>369</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14582,7 +14584,7 @@
         <v>13</v>
       </c>
       <c r="B431" s="7">
-        <v>322</v>
+        <v>704</v>
       </c>
       <c t="s" r="C431" s="7">
         <v>14</v>
@@ -14595,65 +14597,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>17</v>
+        <v>369</v>
       </c>
       <c t="s" r="H431" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I431" s="7">
+        <v>300</v>
+      </c>
+      <c t="s" r="J431" s="7">
         <v>25</v>
-      </c>
-      <c t="s" r="I431" s="7">
-        <v>88</v>
-      </c>
-      <c t="s" r="J431" s="7">
-        <v>333</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
     </row>
     <row r="432" ht="14.25" customHeight="1">
-      <c r="A432" s="6"/>
-      <c r="B432" s="7"/>
-      <c r="C432" s="7"/>
+      <c t="s" r="A432" s="6">
+        <v>13</v>
+      </c>
+      <c r="B432" s="7">
+        <v>878</v>
+      </c>
+      <c t="s" r="C432" s="7">
+        <v>14</v>
+      </c>
       <c r="D432" s="7"/>
-      <c r="E432" s="7"/>
-      <c r="F432" s="7"/>
-      <c r="G432" s="8"/>
-      <c r="H432" s="8"/>
-      <c r="I432" s="7"/>
-      <c r="J432" s="7"/>
+      <c t="s" r="E432" s="7">
+        <v>382</v>
+      </c>
+      <c r="F432" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G432" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H432" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I432" s="7">
+        <v>383</v>
+      </c>
+      <c t="s" r="J432" s="7">
+        <v>319</v>
+      </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c r="M432" s="7"/>
     </row>
     <row r="433" ht="14.25" customHeight="1">
-      <c t="s" r="A433" s="6">
-        <v>13</v>
-      </c>
-      <c r="B433" s="7">
-        <v>720</v>
-      </c>
-      <c t="s" r="C433" s="7">
-        <v>14</v>
-      </c>
+      <c r="A433" s="6"/>
+      <c r="B433" s="7"/>
+      <c r="C433" s="7"/>
       <c r="D433" s="7"/>
-      <c t="s" r="E433" s="7">
-        <v>383</v>
-      </c>
-      <c r="F433" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G433" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="H433" s="8">
-        <v>212</v>
-      </c>
-      <c t="s" r="I433" s="7">
-        <v>153</v>
-      </c>
-      <c t="s" r="J433" s="7">
-        <v>147</v>
-      </c>
+      <c r="E433" s="7"/>
+      <c r="F433" s="7"/>
+      <c r="G433" s="8"/>
+      <c r="H433" s="8"/>
+      <c r="I433" s="7"/>
+      <c r="J433" s="7"/>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c r="M433" s="7"/>
@@ -14663,29 +14665,29 @@
         <v>13</v>
       </c>
       <c r="B434" s="7">
-        <v>721</v>
+        <v>156</v>
       </c>
       <c t="s" r="C434" s="7">
         <v>14</v>
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14696,29 +14698,29 @@
         <v>13</v>
       </c>
       <c r="B435" s="7">
-        <v>703</v>
+        <v>463</v>
       </c>
       <c t="s" r="C435" s="7">
         <v>14</v>
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14729,29 +14731,29 @@
         <v>13</v>
       </c>
       <c r="B436" s="7">
-        <v>704</v>
+        <v>464</v>
       </c>
       <c t="s" r="C436" s="7">
         <v>14</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>300</v>
+        <v>178</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>24</v>
+        <v>287</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14762,45 +14764,63 @@
         <v>13</v>
       </c>
       <c r="B437" s="7">
-        <v>878</v>
+        <v>567</v>
       </c>
       <c t="s" r="C437" s="7">
         <v>14</v>
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>384</v>
+        <v>204</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c r="M437" s="7"/>
     </row>
     <row r="438" ht="14.25" customHeight="1">
-      <c r="A438" s="6"/>
-      <c r="B438" s="7"/>
-      <c r="C438" s="7"/>
+      <c t="s" r="A438" s="6">
+        <v>13</v>
+      </c>
+      <c r="B438" s="7">
+        <v>568</v>
+      </c>
+      <c t="s" r="C438" s="7">
+        <v>14</v>
+      </c>
       <c r="D438" s="7"/>
-      <c r="E438" s="7"/>
-      <c r="F438" s="7"/>
-      <c r="G438" s="8"/>
-      <c r="H438" s="8"/>
-      <c r="I438" s="7"/>
-      <c r="J438" s="7"/>
+      <c t="s" r="E438" s="7">
+        <v>384</v>
+      </c>
+      <c r="F438" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G438" s="8">
+        <v>132</v>
+      </c>
+      <c t="s" r="H438" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I438" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="J438" s="7">
+        <v>28</v>
+      </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c r="M438" s="7"/>
@@ -14810,29 +14830,29 @@
         <v>13</v>
       </c>
       <c r="B439" s="7">
-        <v>156</v>
+        <v>519</v>
       </c>
       <c t="s" r="C439" s="7">
         <v>14</v>
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>85</v>
+        <v>243</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14843,29 +14863,29 @@
         <v>13</v>
       </c>
       <c r="B440" s="7">
-        <v>463</v>
+        <v>522</v>
       </c>
       <c t="s" r="C440" s="7">
         <v>14</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>371</v>
+        <v>34</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14873,66 +14893,48 @@
     </row>
     <row r="441" ht="14.25" customHeight="1">
       <c t="s" r="A441" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B441" s="7">
-        <v>464</v>
+        <v>958</v>
       </c>
       <c t="s" r="C441" s="7">
         <v>14</v>
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
+        <v>384</v>
+      </c>
+      <c r="F441" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G441" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H441" s="8">
+        <v>262</v>
+      </c>
+      <c t="s" r="I441" s="7">
         <v>385</v>
       </c>
-      <c r="F441" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G441" s="8">
-        <v>371</v>
-      </c>
-      <c t="s" r="H441" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I441" s="7">
-        <v>178</v>
-      </c>
       <c t="s" r="J441" s="7">
-        <v>286</v>
+        <v>67</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c r="M441" s="7"/>
     </row>
     <row r="442" ht="14.25" customHeight="1">
-      <c t="s" r="A442" s="6">
-        <v>13</v>
-      </c>
-      <c r="B442" s="7">
-        <v>567</v>
-      </c>
-      <c t="s" r="C442" s="7">
-        <v>14</v>
-      </c>
+      <c r="A442" s="6"/>
+      <c r="B442" s="7"/>
+      <c r="C442" s="7"/>
       <c r="D442" s="7"/>
-      <c t="s" r="E442" s="7">
-        <v>385</v>
-      </c>
-      <c r="F442" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G442" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="H442" s="8">
-        <v>132</v>
-      </c>
-      <c t="s" r="I442" s="7">
-        <v>204</v>
-      </c>
-      <c t="s" r="J442" s="7">
-        <v>175</v>
-      </c>
+      <c r="E442" s="7"/>
+      <c r="F442" s="7"/>
+      <c r="G442" s="8"/>
+      <c r="H442" s="8"/>
+      <c r="I442" s="7"/>
+      <c r="J442" s="7"/>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c r="M442" s="7"/>
@@ -14942,29 +14944,29 @@
         <v>13</v>
       </c>
       <c r="B443" s="7">
-        <v>568</v>
+        <v>801</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F443" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>27</v>
+        <v>377</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14975,29 +14977,29 @@
         <v>13</v>
       </c>
       <c r="B444" s="7">
-        <v>519</v>
+        <v>802</v>
       </c>
       <c t="s" r="C444" s="7">
         <v>14</v>
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F444" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15008,29 +15010,29 @@
         <v>13</v>
       </c>
       <c r="B445" s="7">
-        <v>522</v>
+        <v>278</v>
       </c>
       <c t="s" r="C445" s="7">
         <v>14</v>
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F445" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15038,32 +15040,32 @@
     </row>
     <row r="446" ht="14.25" customHeight="1">
       <c t="s" r="A446" s="6">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B446" s="7">
-        <v>958</v>
+        <v>279</v>
       </c>
       <c t="s" r="C446" s="7">
         <v>14</v>
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F446" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>262</v>
+        <v>26</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>386</v>
+        <v>99</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15102,7 +15104,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>77</v>
@@ -15216,13 +15218,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>87</v>
@@ -15249,10 +15251,10 @@
         <v>330</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>352</v>
@@ -15297,13 +15299,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>162</v>
@@ -15336,10 +15338,10 @@
         <v>392</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15414,10 +15416,10 @@
         <v>394</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>264</v>
@@ -15444,7 +15446,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>394</v>
@@ -15498,7 +15500,7 @@
         <v>396</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J462" s="7">
         <v>204</v>
@@ -15573,7 +15575,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>398</v>
@@ -15590,7 +15592,7 @@
     </row>
     <row r="466" ht="14.25" customHeight="1">
       <c t="s" r="A466" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B466" s="7">
         <v>82</v>
@@ -15609,7 +15611,7 @@
         <v>398</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I466" s="7">
         <v>90</v>
@@ -15654,13 +15656,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>400</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>271</v>
@@ -15690,7 +15692,7 @@
         <v>400</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c t="s" r="I469" s="7">
         <v>401</v>

--- a/Data/FlightPlan/FPL_10SEP26.xlsx
+++ b/Data/FlightPlan/FPL_10SEP26.xlsx
@@ -230,6 +230,9 @@
     <t>22:35</t>
   </si>
   <si>
+    <t>22:55</t>
+  </si>
+  <si>
     <t>23:35</t>
   </si>
   <si>
@@ -260,9 +263,6 @@
     <t>DEL</t>
   </si>
   <si>
-    <t>22:55</t>
-  </si>
-  <si>
     <t>00:05</t>
   </si>
   <si>
@@ -332,309 +332,312 @@
     <t>19:15</t>
   </si>
   <si>
+    <t>21:52</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>01:55</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>00:42</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:04</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>15:09</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>17:13</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:47</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:08</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:16</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>01:55</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>08:39</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:24</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:13</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:48</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>00:42</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:04</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>15:09</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>17:13</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:47</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:08</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:16</t>
-  </si>
-  <si>
-    <t>18:16</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
     <t>22:50</t>
   </si>
   <si>
@@ -983,7 +986,7 @@
     <t>20:41</t>
   </si>
   <si>
-    <t>00:55</t>
+    <t>01:01</t>
   </si>
   <si>
     <t>02:35</t>
@@ -1034,6 +1037,9 @@
     <t>16:44</t>
   </si>
   <si>
+    <t>21:49</t>
+  </si>
+  <si>
     <t>22:15</t>
   </si>
   <si>
@@ -1106,9 +1112,6 @@
     <t>21:05</t>
   </si>
   <si>
-    <t>21:17</t>
-  </si>
-  <si>
     <t>23:25</t>
   </si>
   <si>
@@ -1181,6 +1184,9 @@
     <t>20:59</t>
   </si>
   <si>
+    <t>21:40</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1256,6 +1262,9 @@
     <t>20:50</t>
   </si>
   <si>
+    <t>21:41</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1343,9 +1352,6 @@
     <t>11:11</t>
   </si>
   <si>
-    <t>21:40</t>
-  </si>
-  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -1391,6 +1397,9 @@
     <t>141D</t>
   </si>
   <si>
+    <t>20:22</t>
+  </si>
+  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1484,12 +1493,15 @@
     <t>18:04</t>
   </si>
   <si>
-    <t>20:39</t>
+    <t>20:42</t>
   </si>
   <si>
     <t>23:20</t>
   </si>
   <si>
+    <t>00:35</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1505,6 +1517,147 @@
     <t>18:49</t>
   </si>
   <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>17:43</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>23:03</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>17:51</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>18:59</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>21:48</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>19:08</t>
+  </si>
+  <si>
     <t>23:40</t>
   </si>
   <si>
@@ -1514,147 +1667,6 @@
     <t>00:45</t>
   </si>
   <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>17:43</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>21:57</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>17:27</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>23:07</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>14:56</t>
-  </si>
-  <si>
-    <t>17:51</t>
-  </si>
-  <si>
-    <t>01:34</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>18:59</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>19:21</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>13:23</t>
-  </si>
-  <si>
-    <t>15:49</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>09:24</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>09:17</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>19:08</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1694,6 +1706,9 @@
     <t>18:48</t>
   </si>
   <si>
+    <t>21:07</t>
+  </si>
+  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1733,6 +1748,9 @@
     <t>KJA</t>
   </si>
   <si>
+    <t>20:16</t>
+  </si>
+  <si>
     <t>05:50</t>
   </si>
   <si>
@@ -1751,6 +1769,9 @@
     <t>NQZ</t>
   </si>
   <si>
+    <t>18:39</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1769,6 +1790,9 @@
     <t>15:02</t>
   </si>
   <si>
+    <t>04:47</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1787,7 +1811,7 @@
     <t>Total Record(s): 390</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 10, 2026 19:36</t>
+    <t xml:space="preserve">Generated on  Sep 10, 2026 20:04</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2929,7 +2953,9 @@
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
+      <c t="s" r="M25" s="7">
+        <v>73</v>
+      </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c t="s" r="A26" s="6">
@@ -2955,10 +2981,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2991,7 +3017,7 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -3003,15 +3029,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c t="s" r="M28" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -3026,7 +3052,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -3038,15 +3064,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c t="s" r="M29" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -3061,7 +3087,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -3070,17 +3096,19 @@
         <v>37</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="I30" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c t="s" r="M30" s="7">
+        <v>74</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c t="s" r="A31" s="6">
@@ -3094,13 +3122,13 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>37</v>
@@ -3339,7 +3367,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c t="s" r="J38" s="7">
         <v>108</v>
@@ -3618,7 +3646,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J47" s="7">
         <v>131</v>
@@ -4021,7 +4049,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -4125,7 +4153,9 @@
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
+      <c t="s" r="M63" s="7">
+        <v>159</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c t="s" r="A64" s="6">
@@ -4205,7 +4235,7 @@
         <v>174</v>
       </c>
       <c t="s" r="K66" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
@@ -4566,7 +4596,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>46</v>
@@ -4871,17 +4901,17 @@
         <v>37</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="K86" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4911,7 +4941,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4923,15 +4953,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4946,7 +4976,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4966,7 +4996,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4981,7 +5011,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4993,7 +5023,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>170</v>
@@ -5001,7 +5031,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -5016,7 +5046,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -5028,10 +5058,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -5064,7 +5094,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -5079,12 +5109,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5099,7 +5129,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5111,7 +5141,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>118</v>
@@ -5119,7 +5149,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5134,7 +5164,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5149,12 +5179,12 @@
         <v>114</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5169,7 +5199,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5181,15 +5211,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5204,7 +5234,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5219,12 +5249,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5239,7 +5269,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5259,7 +5289,7 @@
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5274,7 +5304,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5286,17 +5316,17 @@
         <v>32</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="K99" s="7">
         <v>139</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5311,7 +5341,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5323,17 +5353,17 @@
         <v>37</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="K100" s="7">
         <v>140</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5363,7 +5393,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5375,10 +5405,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5398,7 +5428,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5418,7 +5448,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5433,7 +5463,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5453,7 +5483,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5468,7 +5498,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5483,14 +5513,14 @@
         <v>131</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="K105" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5505,7 +5535,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5520,14 +5550,14 @@
         <v>57</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="K106" s="7">
         <v>135</v>
       </c>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5557,7 +5587,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5569,15 +5599,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5592,7 +5622,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5604,15 +5634,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5627,7 +5657,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5639,10 +5669,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5677,7 +5707,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5686,20 +5716,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="K112" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5714,29 +5744,29 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="K113" s="7">
         <v>64</v>
       </c>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5751,7 +5781,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5766,12 +5796,12 @@
         <v>203</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5786,7 +5816,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5798,15 +5828,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5821,7 +5851,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5833,17 +5863,17 @@
         <v>37</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5858,7 +5888,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5870,10 +5900,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5906,7 +5936,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5918,15 +5948,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5941,7 +5971,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5953,7 +5983,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>45</v>
@@ -5961,7 +5991,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5976,7 +6006,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5991,12 +6021,12 @@
         <v>206</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6011,7 +6041,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -6023,7 +6053,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>51</v>
@@ -6059,7 +6089,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6071,7 +6101,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>143</v>
@@ -6079,7 +6109,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6094,7 +6124,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6114,7 +6144,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6129,7 +6159,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6144,7 +6174,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -6164,7 +6194,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6184,7 +6214,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>107</v>
+        <v>208</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -6214,19 +6244,19 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>65</v>
@@ -6234,7 +6264,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6249,7 +6279,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6258,10 +6288,10 @@
         <v>88</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>139</v>
@@ -6269,7 +6299,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6284,29 +6314,29 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="K131" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6321,7 +6351,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6330,13 +6360,13 @@
         <v>88</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6369,7 +6399,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6381,7 +6411,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>92</v>
@@ -6404,7 +6434,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6416,15 +6446,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6439,7 +6469,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6459,7 +6489,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6474,7 +6504,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6493,7 +6523,9 @@
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="6"/>
@@ -6522,7 +6554,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6531,18 +6563,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6557,13 +6589,13 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>28</v>
@@ -6577,7 +6609,7 @@
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6592,7 +6624,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6604,15 +6636,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6627,7 +6659,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6639,7 +6671,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>45</v>
@@ -6647,7 +6679,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6662,7 +6694,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6671,10 +6703,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>147</v>
@@ -6695,22 +6727,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6743,7 +6775,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6758,12 +6790,12 @@
         <v>189</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6778,7 +6810,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6793,12 +6825,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6813,7 +6845,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6822,13 +6854,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6846,22 +6878,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6894,7 +6926,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6909,12 +6941,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6929,7 +6961,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6938,7 +6970,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>120</v>
@@ -6957,20 +6989,20 @@
         <v>13</v>
       </c>
       <c t="s" r="B153" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>17</v>
@@ -6979,12 +7011,12 @@
         <v>205</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6999,7 +7031,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7011,7 +7043,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>205</v>
@@ -7021,7 +7053,7 @@
       </c>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7036,7 +7068,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7051,14 +7083,14 @@
         <v>45</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7073,7 +7105,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7085,17 +7117,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7110,7 +7142,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7125,7 +7157,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -7158,13 +7190,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>28</v>
@@ -7173,14 +7205,14 @@
         <v>126</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="K159" s="7">
         <v>143</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7195,7 +7227,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7210,14 +7242,14 @@
         <v>39</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="K160" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7232,7 +7264,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7244,15 +7276,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7267,7 +7299,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7279,10 +7311,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7315,7 +7347,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7330,12 +7362,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7350,7 +7382,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7362,15 +7394,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7385,7 +7417,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7400,12 +7432,12 @@
         <v>195</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7420,7 +7452,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7432,7 +7464,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>170</v>
@@ -7440,7 +7472,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7470,13 +7502,13 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>37</v>
@@ -7485,7 +7517,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -7505,7 +7537,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7514,18 +7546,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7540,13 +7572,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>37</v>
@@ -7555,12 +7587,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7575,7 +7607,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7590,11 +7622,13 @@
         <v>105</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c t="s" r="M172" s="7">
+        <v>342</v>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
@@ -7608,7 +7642,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7620,10 +7654,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7656,7 +7690,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7676,7 +7710,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7691,7 +7725,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7703,7 +7737,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>89</v>
@@ -7726,7 +7760,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7735,18 +7769,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>190</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7761,22 +7795,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7796,7 +7830,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7808,7 +7842,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>134</v>
@@ -7831,7 +7865,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7846,12 +7880,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7866,7 +7900,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7875,13 +7909,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7914,7 +7948,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7923,10 +7957,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>162</v>
@@ -7934,7 +7968,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7949,13 +7983,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>28</v>
@@ -7964,7 +7998,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7984,7 +8018,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7999,12 +8033,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8019,7 +8053,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8034,12 +8068,12 @@
         <v>203</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8054,7 +8088,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8066,7 +8100,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>174</v>
@@ -8074,7 +8108,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8089,7 +8123,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8104,12 +8138,12 @@
         <v>176</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8124,7 +8158,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8136,10 +8170,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -8157,7 +8191,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8169,7 +8203,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>60</v>
@@ -8205,13 +8239,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>37</v>
@@ -8220,12 +8254,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8240,7 +8274,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8255,12 +8289,12 @@
         <v>205</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8275,7 +8309,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8287,7 +8321,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>68</v>
@@ -8295,7 +8329,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8310,7 +8344,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8325,12 +8359,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>365</v>
+        <v>138</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8345,7 +8379,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8357,10 +8391,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8378,7 +8412,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8393,7 +8427,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -8426,7 +8460,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8438,7 +8472,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>19</v>
@@ -8446,7 +8480,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8461,7 +8495,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8476,7 +8510,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -8496,7 +8530,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8508,7 +8542,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>42</v>
@@ -8531,7 +8565,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8546,12 +8580,12 @@
         <v>205</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8566,7 +8600,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8575,13 +8609,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8599,22 +8633,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8647,7 +8681,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8659,15 +8693,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8682,7 +8716,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8694,7 +8728,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>118</v>
@@ -8702,7 +8736,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8717,7 +8751,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8729,15 +8763,15 @@
         <v>97</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8752,7 +8786,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8767,12 +8801,12 @@
         <v>191</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8787,7 +8821,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8802,7 +8836,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8822,7 +8856,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8837,12 +8871,12 @@
         <v>146</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8857,7 +8891,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8866,13 +8900,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8890,22 +8924,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8938,7 +8972,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8950,7 +8984,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>118</v>
@@ -8973,7 +9007,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8988,12 +9022,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9008,7 +9042,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9020,15 +9054,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9043,7 +9077,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9058,12 +9092,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9078,7 +9112,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9093,12 +9127,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9113,7 +9147,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9128,11 +9162,15 @@
         <v>33</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>374</v>
-      </c>
-      <c r="K220" s="7"/>
+        <v>375</v>
+      </c>
+      <c t="s" r="K220" s="7">
+        <v>391</v>
+      </c>
       <c r="L220" s="7"/>
-      <c r="M220" s="7"/>
+      <c t="s" r="M220" s="7">
+        <v>367</v>
+      </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c r="A221" s="6"/>
@@ -9161,7 +9199,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9181,7 +9219,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9196,7 +9234,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9211,12 +9249,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9246,7 +9284,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9258,15 +9296,15 @@
         <v>93</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9281,7 +9319,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9293,7 +9331,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>165</v>
@@ -9301,7 +9339,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9316,7 +9354,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9331,12 +9369,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9351,7 +9389,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9366,12 +9404,12 @@
         <v>146</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9386,7 +9424,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9395,7 +9433,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>156</v>
@@ -9404,11 +9442,11 @@
         <v>170</v>
       </c>
       <c t="s" r="K229" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9423,25 +9461,25 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c t="s" r="K230" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
@@ -9475,7 +9513,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9487,10 +9525,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9510,7 +9548,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9545,7 +9583,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9557,15 +9595,15 @@
         <v>152</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9580,7 +9618,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9592,7 +9630,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>146</v>
@@ -9600,7 +9638,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9615,7 +9653,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9624,7 +9662,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>168</v>
@@ -9635,7 +9673,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9650,13 +9688,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>28</v>
@@ -9665,7 +9703,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9698,7 +9736,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9713,12 +9751,12 @@
         <v>150</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9733,7 +9771,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9748,12 +9786,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9768,7 +9806,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9777,18 +9815,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9803,13 +9841,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>28</v>
@@ -9818,12 +9856,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9838,7 +9876,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9850,7 +9888,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>178</v>
@@ -9858,7 +9896,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9873,7 +9911,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9885,14 +9923,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
-      <c r="M244" s="7"/>
+      <c t="s" r="M244" s="7">
+        <v>417</v>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
@@ -9906,7 +9946,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9918,10 +9958,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9954,7 +9994,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9966,7 +10006,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>55</v>
@@ -9974,7 +10014,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9989,7 +10029,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10009,7 +10049,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10024,7 +10064,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10046,7 +10086,7 @@
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10061,7 +10101,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10073,17 +10113,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>71</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10098,7 +10138,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10107,13 +10147,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -10131,22 +10171,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -10179,7 +10219,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10199,7 +10239,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10214,7 +10254,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10234,7 +10274,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10249,7 +10289,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10258,18 +10298,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10284,27 +10324,27 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10319,7 +10359,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10328,18 +10368,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10354,19 +10394,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>181</v>
@@ -10402,7 +10442,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10411,18 +10451,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10437,27 +10477,27 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10472,7 +10512,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10484,7 +10524,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>131</v>
@@ -10492,7 +10532,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10507,7 +10547,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10519,7 +10559,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>45</v>
@@ -10527,7 +10567,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10557,7 +10597,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10569,15 +10609,15 @@
         <v>152</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10592,7 +10632,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10607,12 +10647,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10642,7 +10682,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10651,10 +10691,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>117</v>
@@ -10662,7 +10702,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10677,19 +10717,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>64</v>
@@ -10697,7 +10737,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10712,27 +10752,27 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10747,22 +10787,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10782,7 +10822,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10791,13 +10831,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>193</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10817,27 +10857,27 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I274" s="7">
+        <v>266</v>
+      </c>
+      <c t="s" r="J274" s="7">
         <v>265</v>
-      </c>
-      <c t="s" r="J274" s="7">
-        <v>264</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10852,7 +10892,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10867,14 +10907,14 @@
         <v>177</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="K275" s="7">
         <v>71</v>
       </c>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>444</v>
+        <v>391</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10889,7 +10929,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10901,13 +10941,13 @@
         <v>28</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>140</v>
       </c>
       <c t="s" r="K276" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
@@ -10941,7 +10981,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10953,7 +10993,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>126</v>
@@ -10961,7 +11001,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10976,7 +11016,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10991,12 +11031,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11011,7 +11051,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11020,7 +11060,7 @@
         <v>93</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>95</v>
@@ -11031,7 +11071,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11046,19 +11086,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>93</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>26</v>
@@ -11081,7 +11121,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11101,7 +11141,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11131,7 +11171,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -11140,10 +11180,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>64</v>
@@ -11166,19 +11206,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>203</v>
@@ -11186,7 +11226,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11201,7 +11241,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11210,13 +11250,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -11234,22 +11274,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -11282,7 +11322,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11294,10 +11334,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -11317,7 +11357,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11332,12 +11372,12 @@
         <v>118</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11352,7 +11392,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11364,10 +11404,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11387,7 +11427,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11399,15 +11439,15 @@
         <v>88</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11415,14 +11455,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B293" s="7">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11444,7 +11484,7 @@
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>159</v>
+        <v>462</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11474,13 +11514,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>28</v>
@@ -11494,7 +11534,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11509,7 +11549,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11518,7 +11558,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>177</v>
@@ -11544,19 +11584,19 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>199</v>
@@ -11566,7 +11606,7 @@
       </c>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11581,7 +11621,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11593,10 +11633,10 @@
         <v>142</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11629,13 +11669,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>37</v>
@@ -11649,7 +11689,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11664,7 +11704,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11673,18 +11713,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>195</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11699,13 +11739,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>37</v>
@@ -11714,12 +11754,12 @@
         <v>156</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11734,7 +11774,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11743,10 +11783,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>112</v>
@@ -11767,22 +11807,22 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11815,7 +11855,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11827,15 +11867,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11850,7 +11890,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11865,12 +11905,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11885,7 +11925,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11900,12 +11940,12 @@
         <v>203</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11920,7 +11960,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11932,17 +11972,17 @@
         <v>32</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>194</v>
       </c>
       <c t="s" r="K309" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11957,7 +11997,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11977,7 +12017,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11992,7 +12032,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12007,7 +12047,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -12025,7 +12065,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -12040,7 +12080,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -12073,7 +12113,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -12082,18 +12122,18 @@
         <v>37</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12108,27 +12148,27 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12143,7 +12183,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -12155,7 +12195,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>40</v>
@@ -12163,7 +12203,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12178,7 +12218,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -12198,7 +12238,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12213,7 +12253,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12222,7 +12262,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>174</v>
@@ -12233,7 +12273,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12248,27 +12288,27 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12298,7 +12338,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12313,12 +12353,12 @@
         <v>186</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12333,7 +12373,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12345,7 +12385,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>39</v>
@@ -12353,7 +12393,7 @@
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12368,7 +12408,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12377,18 +12417,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12403,27 +12443,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12438,7 +12478,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12447,18 +12487,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12473,19 +12513,19 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>105</v>
@@ -12493,7 +12533,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12508,7 +12548,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12520,14 +12560,18 @@
         <v>184</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>199</v>
       </c>
-      <c r="K327" s="7"/>
+      <c t="s" r="K327" s="7">
+        <v>199</v>
+      </c>
       <c r="L327" s="7"/>
-      <c r="M327" s="7"/>
+      <c t="s" r="M327" s="7">
+        <v>181</v>
+      </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
       <c t="s" r="A328" s="6">
@@ -12541,7 +12585,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12553,14 +12597,18 @@
         <v>28</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>492</v>
-      </c>
-      <c r="K328" s="7"/>
+        <v>495</v>
+      </c>
+      <c t="s" r="K328" s="7">
+        <v>495</v>
+      </c>
       <c r="L328" s="7"/>
-      <c r="M328" s="7"/>
+      <c t="s" r="M328" s="7">
+        <v>496</v>
+      </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
       <c r="A329" s="6"/>
@@ -12589,7 +12637,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12601,7 +12649,7 @@
         <v>152</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>91</v>
@@ -12624,7 +12672,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12636,15 +12684,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12659,7 +12707,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12671,7 +12719,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>176</v>
@@ -12679,7 +12727,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12694,7 +12742,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12703,18 +12751,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12729,13 +12777,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>28</v>
@@ -12744,14 +12792,14 @@
         <v>135</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="K334" s="7">
         <v>71</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12759,14 +12807,14 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>1282</v>
+        <v>858</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12775,58 +12823,50 @@
         <v>28</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>93</v>
+        <v>382</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>198</v>
+        <v>502</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>341</v>
-      </c>
-      <c t="s" r="K335" s="7">
-        <v>444</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="K335" s="7"/>
       <c r="L335" s="7"/>
-      <c t="s" r="M335" s="7">
-        <v>498</v>
-      </c>
+      <c r="M335" s="7"/>
     </row>
     <row r="336" ht="14.25" customHeight="1">
       <c t="s" r="A336" s="6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B336" s="7">
-        <v>1283</v>
+        <v>859</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>93</v>
+        <v>382</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>500</v>
-      </c>
-      <c t="s" r="K336" s="7">
-        <v>453</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c t="s" r="M336" s="7">
-        <v>302</v>
-      </c>
+      <c r="M336" s="7"/>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c r="A337" s="6"/>
@@ -12855,7 +12895,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12864,10 +12904,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>40</v>
@@ -12875,7 +12915,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12890,13 +12930,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>37</v>
@@ -12910,7 +12950,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12925,7 +12965,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12937,7 +12977,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>198</v>
@@ -12960,7 +13000,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12972,10 +13012,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -13008,7 +13048,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13020,7 +13060,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>29</v>
@@ -13028,7 +13068,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13043,7 +13083,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13055,10 +13095,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -13091,7 +13131,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13103,7 +13143,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>153</v>
@@ -13126,7 +13166,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13141,7 +13181,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -13161,7 +13201,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13170,7 +13210,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>155</v>
@@ -13196,13 +13236,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>37</v>
@@ -13211,7 +13251,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -13244,7 +13284,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13253,18 +13293,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13279,13 +13319,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>28</v>
@@ -13314,7 +13354,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13323,18 +13363,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13349,27 +13389,27 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I354" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="J354" s="7">
         <v>234</v>
-      </c>
-      <c t="s" r="J354" s="7">
-        <v>233</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13399,7 +13439,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13411,15 +13451,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13434,7 +13474,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13446,17 +13486,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>39</v>
       </c>
       <c t="s" r="K357" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13471,7 +13511,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13480,18 +13520,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I358" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13506,19 +13546,19 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>104</v>
@@ -13526,7 +13566,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13541,7 +13581,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13550,20 +13590,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="K360" s="7">
         <v>156</v>
       </c>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13578,26 +13618,30 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>309</v>
-      </c>
-      <c r="K361" s="7"/>
+        <v>310</v>
+      </c>
+      <c t="s" r="K361" s="7">
+        <v>237</v>
+      </c>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>256</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c r="A362" s="6"/>
@@ -13626,7 +13670,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13635,18 +13679,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13661,27 +13705,27 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13696,7 +13740,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13705,18 +13749,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13731,19 +13775,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>40</v>
@@ -13751,7 +13795,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13766,7 +13810,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13775,18 +13819,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13801,13 +13845,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>28</v>
@@ -13821,7 +13865,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13836,7 +13880,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13845,10 +13889,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>84</v>
@@ -13858,7 +13902,7 @@
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>523</v>
+        <v>218</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13873,26 +13917,30 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>438</v>
-      </c>
-      <c r="K370" s="7"/>
+        <v>441</v>
+      </c>
+      <c t="s" r="K370" s="7">
+        <v>149</v>
+      </c>
       <c r="L370" s="7"/>
-      <c r="M370" s="7"/>
+      <c t="s" r="M370" s="7">
+        <v>310</v>
+      </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
       <c r="A371" s="6"/>
@@ -13921,7 +13969,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13933,15 +13981,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13956,7 +14004,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13976,7 +14024,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13991,7 +14039,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14011,7 +14059,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14026,7 +14074,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14035,13 +14083,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -14074,7 +14122,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14086,7 +14134,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>98</v>
@@ -14094,7 +14142,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14109,7 +14157,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14144,7 +14192,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14153,10 +14201,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>30</v>
@@ -14164,7 +14212,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14179,29 +14227,29 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c t="s" r="K380" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14231,7 +14279,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14243,7 +14291,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>118</v>
@@ -14266,7 +14314,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -14275,18 +14323,18 @@
         <v>97</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14301,22 +14349,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>97</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -14336,7 +14384,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14351,12 +14399,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14371,7 +14419,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14383,10 +14431,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14406,7 +14454,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14425,7 +14473,9 @@
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
-      <c r="M387" s="7"/>
+      <c t="s" r="M387" s="7">
+        <v>534</v>
+      </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
       <c r="A388" s="6"/>
@@ -14454,7 +14504,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14466,15 +14516,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14489,7 +14539,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14524,7 +14574,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14536,7 +14586,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>42</v>
@@ -14544,7 +14594,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14559,7 +14609,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14574,12 +14624,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14594,7 +14644,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14606,15 +14656,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I393" s="7">
+        <v>266</v>
+      </c>
+      <c t="s" r="J393" s="7">
         <v>265</v>
-      </c>
-      <c t="s" r="J393" s="7">
-        <v>264</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14644,7 +14694,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14659,12 +14709,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14679,7 +14729,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14688,10 +14738,10 @@
         <v>93</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>55</v>
@@ -14699,7 +14749,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14714,27 +14764,27 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>93</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14749,7 +14799,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14758,7 +14808,7 @@
         <v>93</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>131</v>
@@ -14769,7 +14819,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14784,13 +14834,13 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>93</v>
@@ -14799,7 +14849,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14819,7 +14869,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14831,10 +14881,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14867,7 +14917,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14887,7 +14937,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14902,7 +14952,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14917,12 +14967,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14937,7 +14987,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14949,7 +14999,7 @@
         <v>152</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>103</v>
@@ -14957,7 +15007,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14972,7 +15022,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14984,7 +15034,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>206</v>
@@ -14992,7 +15042,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15000,14 +15050,14 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>858</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15016,50 +15066,58 @@
         <v>28</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>381</v>
+        <v>93</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>545</v>
+        <v>198</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>375</v>
-      </c>
-      <c r="K406" s="7"/>
+        <v>343</v>
+      </c>
+      <c t="s" r="K406" s="7">
+        <v>391</v>
+      </c>
       <c r="L406" s="7"/>
-      <c r="M406" s="7"/>
+      <c t="s" r="M406" s="7">
+        <v>549</v>
+      </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
       <c t="s" r="A407" s="6">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>859</v>
+        <v>1283</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>381</v>
+        <v>93</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>547</v>
-      </c>
-      <c r="K407" s="7"/>
+        <v>551</v>
+      </c>
+      <c t="s" r="K407" s="7">
+        <v>455</v>
+      </c>
       <c r="L407" s="7"/>
-      <c r="M407" s="7"/>
+      <c t="s" r="M407" s="7">
+        <v>303</v>
+      </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
       <c r="A408" s="6"/>
@@ -15088,7 +15146,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -15100,7 +15158,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>65</v>
@@ -15108,7 +15166,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15123,7 +15181,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -15143,7 +15201,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15158,7 +15216,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -15178,7 +15236,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15208,7 +15266,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -15228,7 +15286,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15243,7 +15301,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -15263,7 +15321,7 @@
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15293,7 +15351,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15302,10 +15360,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>54</v>
@@ -15313,7 +15371,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15328,27 +15386,27 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15363,7 +15421,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15383,7 +15441,7 @@
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15398,7 +15456,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15407,7 +15465,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>43</v>
@@ -15433,13 +15491,13 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>37</v>
@@ -15448,7 +15506,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15481,7 +15539,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15490,10 +15548,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>202</v>
@@ -15501,7 +15559,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15516,13 +15574,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>37</v>
@@ -15531,12 +15589,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15551,7 +15609,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -15566,7 +15624,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15586,7 +15644,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15598,7 +15656,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>194</v>
@@ -15606,7 +15664,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15621,7 +15679,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15630,10 +15688,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>56</v>
@@ -15643,7 +15701,7 @@
       </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15658,13 +15716,13 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>37</v>
@@ -15676,7 +15734,7 @@
         <v>156</v>
       </c>
       <c t="s" r="K427" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
@@ -15710,22 +15768,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15745,7 +15803,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15754,18 +15812,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15780,13 +15838,13 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>17</v>
@@ -15800,7 +15858,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15815,7 +15873,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15827,14 +15885,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
-      <c r="M432" s="7"/>
+      <c t="s" r="M432" s="7">
+        <v>565</v>
+      </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
       <c r="A433" s="6"/>
@@ -15863,7 +15923,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15875,7 +15935,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>203</v>
@@ -15883,7 +15943,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15898,7 +15958,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15933,7 +15993,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15942,18 +16002,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I436" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15968,19 +16028,19 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>26</v>
@@ -15988,7 +16048,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -16003,7 +16063,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -16015,10 +16075,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -16051,7 +16111,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -16071,7 +16131,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16086,7 +16146,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16095,10 +16155,10 @@
         <v>37</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>40</v>
@@ -16106,7 +16166,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -16121,19 +16181,19 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>102</v>
@@ -16141,7 +16201,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16156,7 +16216,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16168,7 +16228,7 @@
         <v>184</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>57</v>
@@ -16176,7 +16236,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16191,7 +16251,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -16213,7 +16273,7 @@
       </c>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16228,7 +16288,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16240,17 +16300,17 @@
         <v>32</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c t="s" r="K445" s="7">
         <v>157</v>
       </c>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -16265,7 +16325,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16277,17 +16337,17 @@
         <v>37</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>181</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16302,7 +16362,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -16311,13 +16371,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -16350,7 +16410,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -16359,18 +16419,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16385,27 +16445,27 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16420,7 +16480,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16435,12 +16495,12 @@
         <v>153</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16455,7 +16515,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16475,7 +16535,7 @@
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16505,7 +16565,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -16520,12 +16580,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16540,7 +16600,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -16549,18 +16609,18 @@
         <v>88</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>180</v>
+        <v>579</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16575,22 +16635,22 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -16623,7 +16683,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -16635,7 +16695,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J458" s="7">
         <v>120</v>
@@ -16643,7 +16703,7 @@
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16658,7 +16718,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -16706,7 +16766,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
@@ -16718,15 +16778,15 @@
         <v>88</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
       <c t="s" r="M461" s="7">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
@@ -16741,7 +16801,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
@@ -16750,7 +16810,7 @@
         <v>88</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c t="s" r="I462" s="7">
         <v>40</v>
@@ -16761,7 +16821,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>215</v>
+        <v>586</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16776,22 +16836,22 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -16824,13 +16884,13 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>28</v>
@@ -16839,12 +16899,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16859,7 +16919,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -16868,13 +16928,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -16907,7 +16967,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -16916,18 +16976,18 @@
         <v>88</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c t="s" r="I468" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>585</v>
+        <v>592</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -16942,26 +17002,28 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>172</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
-      <c r="M469" s="7"/>
+      <c t="s" r="M469" s="7">
+        <v>593</v>
+      </c>
     </row>
     <row r="470" ht="15" customHeight="1">
       <c r="A470" s="6"/>
@@ -16990,7 +17052,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
@@ -16999,10 +17061,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>72</v>
@@ -17025,22 +17087,22 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c t="s" r="H472" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -17073,7 +17135,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
@@ -17082,13 +17144,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H474" s="8">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c t="s" r="I474" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -17108,22 +17170,22 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -17131,7 +17193,7 @@
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c t="s" r="A476" s="9">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
@@ -17151,7 +17213,7 @@
     <row r="477" ht="65.25" customHeight="1"/>
     <row r="478" ht="16.5" customHeight="1">
       <c t="s" r="A478" s="10">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B478" s="10"/>
       <c r="C478" s="10"/>
@@ -17164,7 +17226,7 @@
       <c r="J478" s="10"/>
       <c r="K478" s="10"/>
       <c t="s" r="L478" s="11">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="M478" s="11"/>
       <c r="N478" s="11"/>
